--- a/sheets/조재수대금교본/검수/조각배.xlsx
+++ b/sheets/조재수대금교본/검수/조각배.xlsx
@@ -3116,8 +3116,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧ㄴ
-△湳</t>
+          <t xml:space="preserve">△湳</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -3142,7 +3141,7 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -3235,7 +3234,7 @@
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="O5" s="24"/>
@@ -3244,7 +3243,7 @@
       <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="S5" s="24"/>
@@ -3338,54 +3337,25 @@
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J8" s="21"/>
       <c r="K8" s="24"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="24"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N8" s="21"/>
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="Q8" s="24"/>
-      <c r="R8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R8" s="21"/>
       <c r="S8" s="24"/>
     </row>
     <row r="9" ht="96.05" customHeight="true">
@@ -3400,7 +3370,7 @@
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南·
-潢⊏∼</t>
+潢∼</t>
         </is>
       </c>
       <c r="E9" s="22"/>
@@ -3420,7 +3390,7 @@
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽
+          <t xml:space="preserve">湳
 –湳</t>
         </is>
       </c>
@@ -3439,13 +3409,13 @@
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∽</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
       <c r="R9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∽</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="S9" s="22"/>
@@ -3463,13 +3433,13 @@
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I10" s="23"/>
@@ -3503,7 +3473,7 @@
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-應∽</t>
+應</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -3543,7 +3513,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -3606,47 +3576,19 @@
         </is>
       </c>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
-      <c r="R14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R14" s="21"/>
       <c r="S14" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/조각배.xlsx
+++ b/sheets/조재수대금교본/검수/조각배.xlsx
@@ -3116,7 +3116,8 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△湳</t>
+          <t xml:space="preserve">∧ㄴ
+△湳</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -3141,7 +3142,7 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -3234,7 +3235,7 @@
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="O5" s="24"/>
@@ -3243,7 +3244,7 @@
       <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="S5" s="24"/>
@@ -3370,7 +3371,7 @@
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南·
-潢∼</t>
+潢⊏∼</t>
         </is>
       </c>
       <c r="E9" s="22"/>
@@ -3390,7 +3391,7 @@
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
+          <t xml:space="preserve">湳∽
 –湳</t>
         </is>
       </c>
@@ -3409,13 +3410,13 @@
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢∽</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
       <c r="R9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢∽</t>
         </is>
       </c>
       <c r="S9" s="22"/>
@@ -3433,13 +3434,13 @@
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="I10" s="23"/>
@@ -3473,7 +3474,7 @@
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-應</t>
+應∽</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -3513,7 +3514,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="O12" s="22"/>

--- a/sheets/조재수대금교본/검수/조각배.xlsx
+++ b/sheets/조재수대금교본/검수/조각배.xlsx
@@ -3043,30 +3043,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="11.63" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="11.63" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="11.63" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="11.63" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.63" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="11.63" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="11.63" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="11.63" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="11.63" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="64.52" customHeight="true">
+    <row r="2" ht="75.47" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="96.05" customHeight="true">
+    <row r="3" ht="112.45" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="96.05" customHeight="true">
+    <row r="4" ht="112.45" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="96.05" customHeight="true">
+    <row r="5" ht="112.45" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="S5" s="24"/>
     </row>
-    <row r="6" ht="96.05" customHeight="true">
+    <row r="6" ht="112.45" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="96.05" customHeight="true">
+    <row r="7" ht="112.45" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
       <c r="R7" s="21"/>
       <c r="S7" s="23"/>
     </row>
-    <row r="8" ht="96.05" customHeight="true">
+    <row r="8" ht="112.45" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="24"/>
     </row>
-    <row r="9" ht="96.05" customHeight="true">
+    <row r="9" ht="112.45" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="96.05" customHeight="true">
+    <row r="10" ht="112.45" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -3459,7 +3459,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="23"/>
     </row>
-    <row r="11" ht="96.05" customHeight="true">
+    <row r="11" ht="112.45" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -3490,7 +3490,7 @@
       <c r="R11" s="21"/>
       <c r="S11" s="24"/>
     </row>
-    <row r="12" ht="96.05" customHeight="true">
+    <row r="12" ht="112.45" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="96.05" customHeight="true">
+    <row r="13" ht="112.45" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" ht="96.05" customHeight="true">
+    <row r="14" ht="112.45" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3598,6 +3598,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="53"/>
 </worksheet>
 </file>